--- a/Investment.xlsx
+++ b/Investment.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30610"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1385" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBAF3003-408A-FE44-80AD-A274CAC83647}"/>
+  <xr:revisionPtr revIDLastSave="1429" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBEFBFCD-E683-4057-A38F-29040935B4F6}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="5" r:id="rId1"/>
@@ -308,7 +308,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;฿&quot;* #,##0.00_-;\-&quot;฿&quot;* #,##0.00_-;_-&quot;฿&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="187" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -626,7 +626,7 @@
       <calculatedColumnFormula>tbl_transactions[[#This Row],[Action]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{E12F4BE4-0B07-4952-A238-606D6354F810}" name="Amount">
-      <calculatedColumnFormula>Transaction_Log!H2</calculatedColumnFormula>
+      <calculatedColumnFormula>tbl_transactions[[#This Row],[Amount]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{64573ADE-EE75-49E8-8D0E-7F56BB772B56}" name="Quantity">
       <calculatedColumnFormula>tbl_transactions[[#This Row],[Quantity]]</calculatedColumnFormula>
@@ -641,7 +641,7 @@
       <calculatedColumnFormula>IF(G2&lt;&gt;0,IF(OR(G2="BUY",G2="SELL"),ROUND((I2*J2)*0.00007,2),0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{A43CEF2A-CC13-492A-AB4F-7C568C787D85}" name="VAT" dataDxfId="6">
-      <calculatedColumnFormula>IF(G2&lt;&gt;0,IF(AND(K2&lt;&gt;"",L2&lt;&gt;"",G2&lt;&gt;"DIVIDEND"),ROUND((K2+L2)*0.07,2),ROUND(H2*0.07,2)),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(G2&lt;&gt;0,IF(AND(K2&lt;&gt;"",L2&lt;&gt;"",G2&lt;&gt;"DIVIDEND"),ROUND((K2+L2)*0.07,2),ROUND(H2*0.1,2)),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{F00759E8-13DB-48F7-A33A-EBE8FD8727FC}" name="Gross Amount" dataDxfId="5">
       <calculatedColumnFormula>IF(F2="cash",0,IF(OR(G2="BUY",G2="SELL"),I2*J2,""))</calculatedColumnFormula>
@@ -680,9 +680,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีม Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -720,7 +720,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -826,7 +826,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -968,7 +968,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -980,7 +980,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -992,7 +992,7 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1004,16 +1004,16 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.48046875" customWidth="1"/>
-    <col min="2" max="2" width="11.61328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.484375" customWidth="1"/>
-    <col min="4" max="4" width="66.1953125" customWidth="1"/>
-    <col min="5" max="7" width="10.61328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="4" max="4" width="66.25" customWidth="1"/>
+    <col min="5" max="7" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>KCG</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -1034,7 +1034,7 @@
         <v>PTT</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1043,7 +1043,7 @@
         <v>SIRI</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
@@ -1051,7 +1051,7 @@
       <c r="C4" s="13"/>
       <c r="D4" s="14"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" s="9" t="s">
         <v>2</v>
       </c>
@@ -1065,13 +1065,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="8" cm="1">
         <f t="array" ref="B6">_xlfn.XLOOKUP(TRUE,tbl__Clean[Cash]&lt;&gt;"",tbl__Clean[Cash],0,0,-1)</f>
-        <v>23</v>
+        <v>4000</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -1080,7 +1080,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="15">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1095,23 +1095,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="8">
         <f>SUMIFS(tbl__Clean[Amount],tbl__Clean[Action],"DEPOSIT")</f>
-        <v>20000</v>
+        <v>24091.3</v>
       </c>
       <c r="C8">
         <f>COUNTIF(tbl__Clean[Action],"DEPOSIT")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="15">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1127,13 +1127,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="16.5">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="8">
         <f>B8-B9</f>
-        <v>20000</v>
+        <v>24091.3</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
@@ -1142,23 +1142,23 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="8">
         <f>SUMIFS(tbl__Clean[Net Amount],tbl__Clean[Action],"DIVIDEND")</f>
-        <v>319.73</v>
+        <v>229.5</v>
       </c>
       <c r="C11">
         <f>COUNTIF(tbl__Clean[Action],"DIVIDEND")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1190,13 +1190,13 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="8">
         <f>SUM(tbl__Clean[Commission])+SUM(tbl__Clean[Fee])+SUM(tbl__Clean[VAT])</f>
-        <v>34.76</v>
+        <v>36.19</v>
       </c>
       <c r="C14">
         <f>C12+C13</f>
@@ -1206,7 +1206,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.5">
       <c r="A18" s="17" t="s">
         <v>25</v>
       </c>
@@ -1217,7 +1217,7 @@
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:7">
       <c r="A19" s="10" t="s">
         <v>26</v>
       </c>
@@ -1240,49 +1240,49 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:7">
       <c r="A20" s="11" t="str">
         <f t="shared" ref="A20:A27" si="0">J1</f>
         <v>KCG</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:7">
       <c r="A21" s="11" t="str">
         <f t="shared" si="0"/>
         <v>PTT</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:7">
       <c r="A22" s="11" t="str">
         <f t="shared" si="0"/>
         <v>SIRI</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:7">
       <c r="A23" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7">
       <c r="A24" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:7">
       <c r="A25" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:7">
       <c r="A26" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:7">
       <c r="A27" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1308,21 +1308,21 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:AD80"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.23828125" customWidth="1"/>
-    <col min="2" max="2" width="10.61328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1171875" customWidth="1"/>
-    <col min="4" max="4" width="10.61328125" customWidth="1"/>
-    <col min="5" max="5" width="5.7421875" customWidth="1"/>
-    <col min="7" max="7" width="20.48046875" customWidth="1"/>
-    <col min="10" max="10" width="6.4921875" customWidth="1"/>
-    <col min="14" max="14" width="12.48828125" customWidth="1"/>
-    <col min="15" max="15" width="11.98828125" customWidth="1"/>
-    <col min="17" max="17" width="12.73828125" customWidth="1"/>
+    <col min="1" max="1" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="5.75" customWidth="1"/>
+    <col min="7" max="7" width="20.5" customWidth="1"/>
+    <col min="10" max="10" width="6.5" customWidth="1"/>
+    <col min="14" max="14" width="12.5" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="17" max="17" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-001</v>
@@ -1405,7 +1405,7 @@
         <v>DEPOSIT</v>
       </c>
       <c r="H2">
-        <f>Transaction_Log!H2</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>4000</v>
       </c>
       <c r="I2">
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <f t="shared" ref="M2:M30" si="2">IF(G2&lt;&gt;0,IF(AND(K2&lt;&gt;"",L2&lt;&gt;"",G2&lt;&gt;"DIVIDEND"),ROUND((K2+L2)*0.07,2),ROUND(H2*0.07,2)),"")</f>
+        <f t="shared" ref="M2:M30" si="2">IF(G2&lt;&gt;0,IF(AND(K2&lt;&gt;"",L2&lt;&gt;"",G2&lt;&gt;"DIVIDEND"),ROUND((K2+L2)*0.07,2),ROUND(H2*0.1,2)),"")</f>
         <v>0</v>
       </c>
       <c r="N2">
@@ -1444,7 +1444,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:18">
       <c r="A3" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-002</v>
@@ -1474,7 +1474,7 @@
         <v>TRANSFER_TO_BROKER</v>
       </c>
       <c r="H3">
-        <f>Transaction_Log!H3</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>4000</v>
       </c>
       <c r="I3">
@@ -1506,7 +1506,7 @@
         <v>4000</v>
       </c>
       <c r="P3">
-        <f>IF(G3&lt;&gt;0,IF(AND(G3="DEPOSIT",F3="cash"),H3+P2,IF(AND(G3="TRANSFER_TO_BROKER",F3="cash"),P2-H3,IF(AND(G3="DIVIDEND",F3&lt;&gt;""),H3+P2,P2))),"")</f>
+        <f>IF(G3&lt;&gt;0,IF(AND(G3="DEPOSIT",F3="cash"),H3+P2,IF(AND(G3="TRANSFER_TO_BROKER",F3="cash"),P2-H3,IF(AND(G3="DIVIDEND",F3&lt;&gt;""),O3+P2,P2))),"")</f>
         <v>0</v>
       </c>
       <c r="Q3">
@@ -1514,7 +1514,7 @@
         <v>4000.02</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:18">
       <c r="A4" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-003</v>
@@ -1544,7 +1544,7 @@
         <v>BUY</v>
       </c>
       <c r="H4">
-        <f>Transaction_Log!H4</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I4">
@@ -1576,7 +1576,7 @@
         <v>450.39999999999992</v>
       </c>
       <c r="P4">
-        <f t="shared" ref="P4:P30" si="5">IF(G4&lt;&gt;0,IF(AND(G4="DEPOSIT",F4="cash"),H4+P3,IF(AND(G4="TRANSFER_TO_BROKER",F4="cash"),P3-H4,IF(AND(G4="DIVIDEND",F4&lt;&gt;""),H4+P3,P3))),"")</f>
+        <f t="shared" ref="P4:P30" si="5">IF(G4&lt;&gt;0,IF(AND(G4="DEPOSIT",F4="cash"),H4+P3,IF(AND(G4="TRANSFER_TO_BROKER",F4="cash"),P3-H4,IF(AND(G4="DIVIDEND",F4&lt;&gt;""),O4+P3,P3))),"")</f>
         <v>0</v>
       </c>
       <c r="Q4">
@@ -1584,7 +1584,7 @@
         <v>3549.62</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:18">
       <c r="A5" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-004</v>
@@ -1614,7 +1614,7 @@
         <v>BUY</v>
       </c>
       <c r="H5">
-        <f>Transaction_Log!H6</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I5">
@@ -1657,7 +1657,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:18">
       <c r="A6" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-005</v>
@@ -1687,7 +1687,7 @@
         <v>BUY</v>
       </c>
       <c r="H6">
-        <f>Transaction_Log!H5</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I6">
@@ -1727,7 +1727,7 @@
         <v>143.62999999999977</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:18">
       <c r="A7" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-006</v>
@@ -1757,7 +1757,7 @@
         <v>BUY</v>
       </c>
       <c r="H7">
-        <f>Transaction_Log!H7</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I7">
@@ -1797,7 +1797,7 @@
         <v>0.49999999999977263</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:18">
       <c r="A8" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-007</v>
@@ -1827,7 +1827,7 @@
         <v>DIVIDEND</v>
       </c>
       <c r="H8">
-        <f>Transaction_Log!H8</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>90</v>
       </c>
       <c r="I8">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="M8">
         <f t="shared" si="2"/>
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="3"/>
@@ -1856,18 +1856,18 @@
       </c>
       <c r="O8">
         <f t="shared" si="4"/>
-        <v>83.7</v>
+        <v>81</v>
       </c>
       <c r="P8">
         <f t="shared" si="5"/>
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="Q8">
         <f t="shared" si="6"/>
         <v>0.49999999999977263</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:18">
       <c r="A9" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-008</v>
@@ -1897,7 +1897,7 @@
         <v>DIVIDEND</v>
       </c>
       <c r="H9">
-        <f>Transaction_Log!H9</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>140</v>
       </c>
       <c r="I9">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="M9">
         <f t="shared" si="2"/>
-        <v>9.8000000000000007</v>
+        <v>14</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="3"/>
@@ -1926,18 +1926,18 @@
       </c>
       <c r="O9">
         <f t="shared" si="4"/>
-        <v>130.19999999999999</v>
+        <v>126</v>
       </c>
       <c r="P9">
         <f t="shared" si="5"/>
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="Q9">
         <f t="shared" si="6"/>
         <v>0.49999999999977263</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:18">
       <c r="A10" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-009</v>
@@ -1967,7 +1967,7 @@
         <v>DEPOSIT</v>
       </c>
       <c r="H10">
-        <f>Transaction_Log!H10</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>4000</v>
       </c>
       <c r="I10">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="P10">
         <f t="shared" si="5"/>
-        <v>4230</v>
+        <v>4207</v>
       </c>
       <c r="Q10">
         <f t="shared" si="6"/>
         <v>0.49999999999977263</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:18">
       <c r="A11" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-010</v>
@@ -2037,7 +2037,7 @@
         <v>DEPOSIT</v>
       </c>
       <c r="H11">
-        <f>Transaction_Log!H11</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>4000</v>
       </c>
       <c r="I11">
@@ -2070,14 +2070,14 @@
       </c>
       <c r="P11">
         <f t="shared" si="5"/>
-        <v>8230</v>
+        <v>8207</v>
       </c>
       <c r="Q11">
         <f t="shared" si="6"/>
         <v>0.49999999999977263</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:18">
       <c r="A12" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-011</v>
@@ -2107,7 +2107,7 @@
         <v>DEPOSIT</v>
       </c>
       <c r="H12">
-        <f>Transaction_Log!H12</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>4000</v>
       </c>
       <c r="I12">
@@ -2140,14 +2140,14 @@
       </c>
       <c r="P12">
         <f t="shared" si="5"/>
-        <v>12230</v>
+        <v>12207</v>
       </c>
       <c r="Q12">
         <f t="shared" si="6"/>
         <v>0.49999999999977263</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:18">
       <c r="A13" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-012</v>
@@ -2177,7 +2177,7 @@
         <v>SELL</v>
       </c>
       <c r="H13">
-        <f>Transaction_Log!H13</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I13">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="P13">
         <f t="shared" si="5"/>
-        <v>12230</v>
+        <v>12207</v>
       </c>
       <c r="Q13">
         <f t="shared" si="6"/>
         <v>4171.84</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:18">
       <c r="A14" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-013</v>
@@ -2247,7 +2247,7 @@
         <v>BUY</v>
       </c>
       <c r="H14">
-        <f>Transaction_Log!H14</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I14">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="P14">
         <f t="shared" si="5"/>
-        <v>12230</v>
+        <v>12207</v>
       </c>
       <c r="Q14">
         <f t="shared" si="6"/>
         <v>168.32999999999993</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:18">
       <c r="A15" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-014</v>
@@ -2317,8 +2317,8 @@
         <v>DIVIDEND</v>
       </c>
       <c r="H15">
-        <f>Transaction_Log!H15</f>
-        <v>22.5</v>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
+        <v>25</v>
       </c>
       <c r="I15">
         <f>tbl_transactions[[#This Row],[Quantity]]</f>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="M15">
         <f t="shared" si="2"/>
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="3"/>
@@ -2346,18 +2346,18 @@
       </c>
       <c r="O15">
         <f t="shared" si="4"/>
-        <v>20.92</v>
+        <v>22.5</v>
       </c>
       <c r="P15">
         <f t="shared" si="5"/>
-        <v>12252.5</v>
+        <v>12229.5</v>
       </c>
       <c r="Q15">
         <f t="shared" si="6"/>
         <v>168.32999999999993</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:18">
       <c r="A16" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-015</v>
@@ -2387,7 +2387,7 @@
         <v>DEPOSIT</v>
       </c>
       <c r="H16">
-        <f>Transaction_Log!H16</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>4000</v>
       </c>
       <c r="I16">
@@ -2420,14 +2420,14 @@
       </c>
       <c r="P16">
         <f t="shared" si="5"/>
-        <v>16252.5</v>
+        <v>16229.5</v>
       </c>
       <c r="Q16">
         <f t="shared" si="6"/>
         <v>168.32999999999993</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:30">
       <c r="A17" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-016</v>
@@ -2454,10 +2454,10 @@
       </c>
       <c r="G17" t="str">
         <f>tbl_transactions[[#This Row],[Action]]</f>
-        <v>DIVIDEND</v>
+        <v>DEPOSIT</v>
       </c>
       <c r="H17">
-        <f>Transaction_Log!H17</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>91.3</v>
       </c>
       <c r="I17">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="M17">
         <f t="shared" si="2"/>
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="N17">
         <f t="shared" si="3"/>
@@ -2486,18 +2486,18 @@
       </c>
       <c r="O17">
         <f t="shared" si="4"/>
-        <v>84.91</v>
+        <v>91.3</v>
       </c>
       <c r="P17">
         <f t="shared" si="5"/>
-        <v>16343.8</v>
+        <v>16320.8</v>
       </c>
       <c r="Q17">
         <f t="shared" si="6"/>
         <v>168.32999999999993</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:30">
       <c r="A18" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-017</v>
@@ -2527,7 +2527,7 @@
         <v>TRANSFER_TO_BROKER</v>
       </c>
       <c r="H18">
-        <f>Transaction_Log!H18</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>16320.8</v>
       </c>
       <c r="I18">
@@ -2560,14 +2560,14 @@
       </c>
       <c r="P18">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q18">
         <f t="shared" si="6"/>
         <v>16489.129999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:30">
       <c r="A19" s="1" t="str">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>TH-018</v>
@@ -2597,8 +2597,8 @@
         <v>DEPOSIT</v>
       </c>
       <c r="H19">
-        <f>Transaction_Log!H51</f>
-        <v>0</v>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
+        <v>4000</v>
       </c>
       <c r="I19">
         <f>tbl_transactions[[#This Row],[Quantity]]</f>
@@ -2626,18 +2626,18 @@
       </c>
       <c r="O19">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="P19">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>4000</v>
       </c>
       <c r="Q19">
         <f t="shared" si="6"/>
         <v>16489.129999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:30">
       <c r="A20" s="1">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <f>Transaction_Log!H52</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I20">
@@ -2707,7 +2707,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:30">
       <c r="A21" s="1">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <f>Transaction_Log!H53</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I21">
@@ -2777,7 +2777,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:30">
       <c r="A22" s="1">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>0</v>
@@ -2807,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <f>Transaction_Log!H54</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I22">
@@ -2847,7 +2847,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:30">
       <c r="A23" s="1">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>0</v>
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <f>Transaction_Log!H55</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I23">
@@ -2917,7 +2917,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:30">
       <c r="A24" s="1">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>0</v>
@@ -2947,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <f>Transaction_Log!H56</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I24">
@@ -2987,7 +2987,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:30">
       <c r="A25" s="1">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>0</v>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <f>Transaction_Log!H57</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I25">
@@ -3057,7 +3057,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:30">
       <c r="A26" s="1">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>0</v>
@@ -3087,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <f>Transaction_Log!H58</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I26">
@@ -3127,7 +3127,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:30">
       <c r="A27" s="1">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>0</v>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <f>Transaction_Log!H59</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I27">
@@ -3197,7 +3197,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:30">
       <c r="A28" s="1">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <f>Transaction_Log!H60</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I28">
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:30">
       <c r="A29" s="1">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>0</v>
@@ -3297,7 +3297,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <f>Transaction_Log!H61</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I29">
@@ -3337,7 +3337,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:30">
       <c r="A30" s="1">
         <f>tbl_transactions[[#This Row],[Transaction ID]]</f>
         <v>0</v>
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <f>Transaction_Log!H62</f>
+        <f>tbl_transactions[[#This Row],[Amount]]</f>
         <v>0</v>
       </c>
       <c r="I30">
@@ -3407,7 +3407,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:30">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3439,7 +3439,7 @@
       <c r="AC31" s="2"/>
       <c r="AD31" s="2"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:30">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3471,7 +3471,7 @@
       <c r="AC32" s="2"/>
       <c r="AD32" s="2"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:30">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3503,7 +3503,7 @@
       <c r="AC33" s="2"/>
       <c r="AD33" s="2"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:30">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3535,7 +3535,7 @@
       <c r="AC34" s="2"/>
       <c r="AD34" s="2"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:30">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3567,7 +3567,7 @@
       <c r="AC35" s="2"/>
       <c r="AD35" s="2"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:30">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3599,7 +3599,7 @@
       <c r="AC36" s="2"/>
       <c r="AD36" s="2"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:30">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -3631,7 +3631,7 @@
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:30">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -3663,7 +3663,7 @@
       <c r="AC38" s="2"/>
       <c r="AD38" s="2"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:30">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -3695,7 +3695,7 @@
       <c r="AC39" s="2"/>
       <c r="AD39" s="2"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:30">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -3727,7 +3727,7 @@
       <c r="AC40" s="2"/>
       <c r="AD40" s="2"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:30">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -3759,7 +3759,7 @@
       <c r="AC41" s="2"/>
       <c r="AD41" s="2"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:30">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -3791,7 +3791,7 @@
       <c r="AC42" s="2"/>
       <c r="AD42" s="2"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:30">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3823,7 +3823,7 @@
       <c r="AC43" s="2"/>
       <c r="AD43" s="2"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:30">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3855,7 +3855,7 @@
       <c r="AC44" s="2"/>
       <c r="AD44" s="2"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:30">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -3887,7 +3887,7 @@
       <c r="AC45" s="2"/>
       <c r="AD45" s="2"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:30">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3919,7 +3919,7 @@
       <c r="AC46" s="2"/>
       <c r="AD46" s="2"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:30">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -3951,7 +3951,7 @@
       <c r="AC47" s="2"/>
       <c r="AD47" s="2"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:30">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3983,7 +3983,7 @@
       <c r="AC48" s="2"/>
       <c r="AD48" s="2"/>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:30">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4015,7 +4015,7 @@
       <c r="AC49" s="2"/>
       <c r="AD49" s="2"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:30">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -4047,7 +4047,7 @@
       <c r="AC50" s="2"/>
       <c r="AD50" s="2"/>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:30">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -4079,7 +4079,7 @@
       <c r="AC51" s="2"/>
       <c r="AD51" s="2"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:30">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -4111,7 +4111,7 @@
       <c r="AC52" s="2"/>
       <c r="AD52" s="2"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:30">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -4143,7 +4143,7 @@
       <c r="AC53" s="2"/>
       <c r="AD53" s="2"/>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:30">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -4175,7 +4175,7 @@
       <c r="AC54" s="2"/>
       <c r="AD54" s="2"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:30">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -4207,7 +4207,7 @@
       <c r="AC55" s="2"/>
       <c r="AD55" s="2"/>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:30">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -4239,7 +4239,7 @@
       <c r="AC56" s="2"/>
       <c r="AD56" s="2"/>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:30">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -4271,7 +4271,7 @@
       <c r="AC57" s="2"/>
       <c r="AD57" s="2"/>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:30">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -4303,7 +4303,7 @@
       <c r="AC58" s="2"/>
       <c r="AD58" s="2"/>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:30">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -4335,7 +4335,7 @@
       <c r="AC59" s="2"/>
       <c r="AD59" s="2"/>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:30">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -4367,7 +4367,7 @@
       <c r="AC60" s="2"/>
       <c r="AD60" s="2"/>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:30">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -4399,7 +4399,7 @@
       <c r="AC61" s="2"/>
       <c r="AD61" s="2"/>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:30">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -4431,7 +4431,7 @@
       <c r="AC62" s="2"/>
       <c r="AD62" s="2"/>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:30">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -4463,7 +4463,7 @@
       <c r="AC63" s="2"/>
       <c r="AD63" s="2"/>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:30">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -4495,7 +4495,7 @@
       <c r="AC64" s="2"/>
       <c r="AD64" s="2"/>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:30">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -4527,7 +4527,7 @@
       <c r="AC65" s="2"/>
       <c r="AD65" s="2"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:30">
       <c r="C66" s="3"/>
       <c r="G66" s="1"/>
       <c r="K66" t="str">
@@ -4559,7 +4559,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:30">
       <c r="C67" s="3"/>
       <c r="G67" s="1"/>
       <c r="K67" t="str">
@@ -4591,7 +4591,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:30">
       <c r="C68" s="3"/>
       <c r="G68" s="1"/>
       <c r="K68" t="str">
@@ -4623,7 +4623,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:30">
       <c r="C69" s="3"/>
       <c r="G69" s="1"/>
       <c r="K69" t="str">
@@ -4652,7 +4652,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:30">
       <c r="C70" s="3"/>
       <c r="G70" s="1"/>
       <c r="K70" t="str">
@@ -4681,7 +4681,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:30">
       <c r="C71" s="3"/>
       <c r="G71" s="1"/>
       <c r="K71" t="str">
@@ -4710,7 +4710,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:30">
       <c r="C72" s="3"/>
       <c r="G72" s="1"/>
       <c r="K72" t="str">
@@ -4742,7 +4742,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:30">
       <c r="C73" s="3"/>
       <c r="G73" s="1"/>
       <c r="K73" t="str">
@@ -4774,7 +4774,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:30">
       <c r="C74" s="3"/>
       <c r="G74" s="1"/>
       <c r="K74" t="str">
@@ -4806,7 +4806,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:30">
       <c r="C75" s="3"/>
       <c r="G75" s="1"/>
       <c r="K75" t="str">
@@ -4838,7 +4838,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:30">
       <c r="C76" s="3"/>
       <c r="G76" s="1"/>
       <c r="K76" t="str">
@@ -4870,7 +4870,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:30">
       <c r="C77" s="3"/>
       <c r="G77" s="1"/>
       <c r="K77" t="str">
@@ -4902,7 +4902,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:30">
       <c r="C78" s="3"/>
       <c r="G78" s="1"/>
       <c r="K78" t="str">
@@ -4934,7 +4934,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:30">
       <c r="C79" s="3"/>
       <c r="G79" s="1"/>
       <c r="K79" t="str">
@@ -4966,7 +4966,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:30">
       <c r="C80" s="3"/>
       <c r="G80" s="1"/>
       <c r="K80" t="str">
@@ -5008,7 +5008,7 @@
       <formula1>0</formula1>
       <formula2>100000000000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H30 I1:I30 I66:I1048576" xr:uid="{25489990-3F26-438A-ACCF-17727C242C32}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I66:I1048576 I1:I30 H2:H30" xr:uid="{25489990-3F26-438A-ACCF-17727C242C32}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -5023,19 +5023,19 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.86328125" customWidth="1"/>
-    <col min="2" max="2" width="10.61328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.61328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.60546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.61328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.1171875" customWidth="1"/>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
+    <col min="2" max="2" width="10.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>65</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -5312,7 +5312,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>69</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>41.75</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -5390,7 +5390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -5410,10 +5410,10 @@
         <v>64</v>
       </c>
       <c r="H15">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>74</v>
       </c>
@@ -5433,7 +5433,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -5447,13 +5447,13 @@
         <v>51</v>
       </c>
       <c r="G17" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H17">
         <v>91.3</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>16320.8</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>77</v>
       </c>
